--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,32 +618,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RLE / unique ratio</t>
+          <t>RLE duration</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>no freeze</t>
+          <t>&lt;15 min</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>&lt;5 min</t>
+          <t>15–30 min</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5–15 min</t>
+          <t>30–60 min</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15–60 min</t>
+          <t>60–360 min</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&gt;60 min</t>
+          <t>≥360 min</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
@@ -532,7 +532,8 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>very frequent (&gt;20%)</t>
+          <t>very frequent
+(&gt;20%)</t>
         </is>
       </c>
     </row>
@@ -569,7 +570,8 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>high (sustained)</t>
+          <t>high
+(sustained)</t>
         </is>
       </c>
     </row>
@@ -606,7 +608,8 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&gt; 3.0 sustained</t>
+          <t>&gt; 3.0
+sustained</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig1_D1_dimension_matrix_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
